--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_06-08-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_06-08-2025.xlsx
@@ -589,27 +589,27 @@
       <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff654f46b55+79621]
+	GetHandleVerifier [0x0x7ff654f46bb0+79712]
+	(No symbol) [0x0x7ff654cdc0ea]
+	(No symbol) [0x0x7ff654d32f56]
+	(No symbol) [0x0x7ff654d3320c]
+	(No symbol) [0x0x7ff654d865b7]
+	(No symbol) [0x0x7ff654d5b17f]
+	(No symbol) [0x0x7ff654d833d0]
+	(No symbol) [0x0x7ff654d5af13]
+	(No symbol) [0x0x7ff654d24151]
+	(No symbol) [0x0x7ff654d24ee3]
+	GetHandleVerifier [0x0x7ff65520686d+2962461]
+	GetHandleVerifier [0x0x7ff655200b8d+2938685]
+	GetHandleVerifier [0x0x7ff65521f74d+3064573]
+	GetHandleVerifier [0x0x7ff654f60c9e+186446]
+	GetHandleVerifier [0x0x7ff654f68a6f+218655]
+	GetHandleVerifier [0x0x7ff654f4f944+115956]
+	GetHandleVerifier [0x0x7ff654f4faf9+116393]
+	GetHandleVerifier [0x0x7ff654f35f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -659,78 +659,78 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>£12.33</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>£12.33</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>£12.33</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>£12.80</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>£12.62</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>£12.62</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>£13.33</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>£12.83</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>£12.33</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>£12.62</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>£12.80</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>£12.62</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>£12.62</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>£13.33</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>£12.83</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>£12.33</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>£12.62</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff654f46b55+79621]
+	GetHandleVerifier [0x0x7ff654f46bb0+79712]
+	(No symbol) [0x0x7ff654cdc0ea]
+	(No symbol) [0x0x7ff654d32f56]
+	(No symbol) [0x0x7ff654d3320c]
+	(No symbol) [0x0x7ff654d865b7]
+	(No symbol) [0x0x7ff654d5b17f]
+	(No symbol) [0x0x7ff654d833d0]
+	(No symbol) [0x0x7ff654d5af13]
+	(No symbol) [0x0x7ff654d24151]
+	(No symbol) [0x0x7ff654d24ee3]
+	GetHandleVerifier [0x0x7ff65520686d+2962461]
+	GetHandleVerifier [0x0x7ff655200b8d+2938685]
+	GetHandleVerifier [0x0x7ff65521f74d+3064573]
+	GetHandleVerifier [0x0x7ff654f60c9e+186446]
+	GetHandleVerifier [0x0x7ff654f68a6f+218655]
+	GetHandleVerifier [0x0x7ff654f4f944+115956]
+	GetHandleVerifier [0x0x7ff654f4faf9+116393]
+	GetHandleVerifier [0x0x7ff654f35f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -780,78 +780,78 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>£15.75</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>£15.75</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>£15.75</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>£16.50</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>£15.99</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>£16.18</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>£18.00</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>£16.46</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>£15.75</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>£16.18</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>£16.18</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>£16.50</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>£15.99</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>£16.18</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>£18.00</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>£16.46</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>£15.75</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>£16.18</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff654f46b55+79621]
+	GetHandleVerifier [0x0x7ff654f46bb0+79712]
+	(No symbol) [0x0x7ff654cdc0ea]
+	(No symbol) [0x0x7ff654d32f56]
+	(No symbol) [0x0x7ff654d3320c]
+	(No symbol) [0x0x7ff654d865b7]
+	(No symbol) [0x0x7ff654d5b17f]
+	(No symbol) [0x0x7ff654d833d0]
+	(No symbol) [0x0x7ff654d5af13]
+	(No symbol) [0x0x7ff654d24151]
+	(No symbol) [0x0x7ff654d24ee3]
+	GetHandleVerifier [0x0x7ff65520686d+2962461]
+	GetHandleVerifier [0x0x7ff655200b8d+2938685]
+	GetHandleVerifier [0x0x7ff65521f74d+3064573]
+	GetHandleVerifier [0x0x7ff654f60c9e+186446]
+	GetHandleVerifier [0x0x7ff654f68a6f+218655]
+	GetHandleVerifier [0x0x7ff654f4f944+115956]
+	GetHandleVerifier [0x0x7ff654f4faf9+116393]
+	GetHandleVerifier [0x0x7ff654f35f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -906,29 +906,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>£16.50</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>£16.50</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>£16.65</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>£16.60</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>£16.60</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>£16.65</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>£16.60</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>£16.60</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>£17.48</t>
@@ -952,27 +952,27 @@
       <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff654f46b55+79621]
+	GetHandleVerifier [0x0x7ff654f46bb0+79712]
+	(No symbol) [0x0x7ff654cdc0ea]
+	(No symbol) [0x0x7ff654d32f56]
+	(No symbol) [0x0x7ff654d3320c]
+	(No symbol) [0x0x7ff654d865b7]
+	(No symbol) [0x0x7ff654d5b17f]
+	(No symbol) [0x0x7ff654d833d0]
+	(No symbol) [0x0x7ff654d5af13]
+	(No symbol) [0x0x7ff654d24151]
+	(No symbol) [0x0x7ff654d24ee3]
+	GetHandleVerifier [0x0x7ff65520686d+2962461]
+	GetHandleVerifier [0x0x7ff655200b8d+2938685]
+	GetHandleVerifier [0x0x7ff65521f74d+3064573]
+	GetHandleVerifier [0x0x7ff654f60c9e+186446]
+	GetHandleVerifier [0x0x7ff654f68a6f+218655]
+	GetHandleVerifier [0x0x7ff654f4f944+115956]
+	GetHandleVerifier [0x0x7ff654f4faf9+116393]
+	GetHandleVerifier [0x0x7ff654f35f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1022,78 +1022,78 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>£21.00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>£21.00</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>£21.00</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>£21.20</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>£21.05</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>£21.08</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>£24.48</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>£21.46</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>£20.60</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>£21.08</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>£21.08</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>£21.20</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>£21.05</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>£21.08</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>£24.48</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>£21.46</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>£20.60</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>£21.08</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff654f46b55+79621]
+	GetHandleVerifier [0x0x7ff654f46bb0+79712]
+	(No symbol) [0x0x7ff654cdc0ea]
+	(No symbol) [0x0x7ff654d32f56]
+	(No symbol) [0x0x7ff654d3320c]
+	(No symbol) [0x0x7ff654d865b7]
+	(No symbol) [0x0x7ff654d5b17f]
+	(No symbol) [0x0x7ff654d833d0]
+	(No symbol) [0x0x7ff654d5af13]
+	(No symbol) [0x0x7ff654d24151]
+	(No symbol) [0x0x7ff654d24ee3]
+	GetHandleVerifier [0x0x7ff65520686d+2962461]
+	GetHandleVerifier [0x0x7ff655200b8d+2938685]
+	GetHandleVerifier [0x0x7ff65521f74d+3064573]
+	GetHandleVerifier [0x0x7ff654f60c9e+186446]
+	GetHandleVerifier [0x0x7ff654f68a6f+218655]
+	GetHandleVerifier [0x0x7ff654f4f944+115956]
+	GetHandleVerifier [0x0x7ff654f4faf9+116393]
+	GetHandleVerifier [0x0x7ff654f35f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1194,27 +1194,27 @@
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff654f46b55+79621]
+	GetHandleVerifier [0x0x7ff654f46bb0+79712]
+	(No symbol) [0x0x7ff654cdc0ea]
+	(No symbol) [0x0x7ff654d32f56]
+	(No symbol) [0x0x7ff654d3320c]
+	(No symbol) [0x0x7ff654d865b7]
+	(No symbol) [0x0x7ff654d5b17f]
+	(No symbol) [0x0x7ff654d833d0]
+	(No symbol) [0x0x7ff654d5af13]
+	(No symbol) [0x0x7ff654d24151]
+	(No symbol) [0x0x7ff654d24ee3]
+	GetHandleVerifier [0x0x7ff65520686d+2962461]
+	GetHandleVerifier [0x0x7ff655200b8d+2938685]
+	GetHandleVerifier [0x0x7ff65521f74d+3064573]
+	GetHandleVerifier [0x0x7ff654f60c9e+186446]
+	GetHandleVerifier [0x0x7ff654f68a6f+218655]
+	GetHandleVerifier [0x0x7ff654f4f944+115956]
+	GetHandleVerifier [0x0x7ff654f4faf9+116393]
+	GetHandleVerifier [0x0x7ff654f35f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1315,27 +1315,27 @@
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff654f46b55+79621]
+	GetHandleVerifier [0x0x7ff654f46bb0+79712]
+	(No symbol) [0x0x7ff654cdc0ea]
+	(No symbol) [0x0x7ff654d32f56]
+	(No symbol) [0x0x7ff654d3320c]
+	(No symbol) [0x0x7ff654d865b7]
+	(No symbol) [0x0x7ff654d5b17f]
+	(No symbol) [0x0x7ff654d833d0]
+	(No symbol) [0x0x7ff654d5af13]
+	(No symbol) [0x0x7ff654d24151]
+	(No symbol) [0x0x7ff654d24ee3]
+	GetHandleVerifier [0x0x7ff65520686d+2962461]
+	GetHandleVerifier [0x0x7ff655200b8d+2938685]
+	GetHandleVerifier [0x0x7ff65521f74d+3064573]
+	GetHandleVerifier [0x0x7ff654f60c9e+186446]
+	GetHandleVerifier [0x0x7ff654f68a6f+218655]
+	GetHandleVerifier [0x0x7ff654f4f944+115956]
+	GetHandleVerifier [0x0x7ff654f4faf9+116393]
+	GetHandleVerifier [0x0x7ff654f35f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1385,34 +1385,34 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>£26.40</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>£26.40</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>£26.40</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>£26.50</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>£26.45</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>£26.50</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>£26.50</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>£26.50</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>£26.45</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>£26.50</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>£27.62</t>
@@ -1436,27 +1436,27 @@
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff654f46b55+79621]
+	GetHandleVerifier [0x0x7ff654f46bb0+79712]
+	(No symbol) [0x0x7ff654cdc0ea]
+	(No symbol) [0x0x7ff654d32f56]
+	(No symbol) [0x0x7ff654d3320c]
+	(No symbol) [0x0x7ff654d865b7]
+	(No symbol) [0x0x7ff654d5b17f]
+	(No symbol) [0x0x7ff654d833d0]
+	(No symbol) [0x0x7ff654d5af13]
+	(No symbol) [0x0x7ff654d24151]
+	(No symbol) [0x0x7ff654d24ee3]
+	GetHandleVerifier [0x0x7ff65520686d+2962461]
+	GetHandleVerifier [0x0x7ff655200b8d+2938685]
+	GetHandleVerifier [0x0x7ff65521f74d+3064573]
+	GetHandleVerifier [0x0x7ff654f60c9e+186446]
+	GetHandleVerifier [0x0x7ff654f68a6f+218655]
+	GetHandleVerifier [0x0x7ff654f4f944+115956]
+	GetHandleVerifier [0x0x7ff654f4faf9+116393]
+	GetHandleVerifier [0x0x7ff654f35f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1506,78 +1506,78 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>£28.80</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>£28.80</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>£28.80</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>£28.80</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>£28.80</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>£28.82</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>£31.00</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>£29.33</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>£27.95</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>£28.82</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>£28.82</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>£28.80</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>£28.80</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>£28.82</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>£31.00</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>£29.33</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>£27.95</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>£28.82</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff654f46b55+79621]
+	GetHandleVerifier [0x0x7ff654f46bb0+79712]
+	(No symbol) [0x0x7ff654cdc0ea]
+	(No symbol) [0x0x7ff654d32f56]
+	(No symbol) [0x0x7ff654d3320c]
+	(No symbol) [0x0x7ff654d865b7]
+	(No symbol) [0x0x7ff654d5b17f]
+	(No symbol) [0x0x7ff654d833d0]
+	(No symbol) [0x0x7ff654d5af13]
+	(No symbol) [0x0x7ff654d24151]
+	(No symbol) [0x0x7ff654d24ee3]
+	GetHandleVerifier [0x0x7ff65520686d+2962461]
+	GetHandleVerifier [0x0x7ff655200b8d+2938685]
+	GetHandleVerifier [0x0x7ff65521f74d+3064573]
+	GetHandleVerifier [0x0x7ff654f60c9e+186446]
+	GetHandleVerifier [0x0x7ff654f68a6f+218655]
+	GetHandleVerifier [0x0x7ff654f4f944+115956]
+	GetHandleVerifier [0x0x7ff654f4faf9+116393]
+	GetHandleVerifier [0x0x7ff654f35f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1627,34 +1627,34 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>£28.35</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>£28.35</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>£28.35</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>£28.50</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>£28.60</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>£28.50</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>£28.50</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>£28.50</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>£28.60</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>£28.50</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>£31.00</t>
@@ -1678,27 +1678,27 @@
       <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff654f46b55+79621]
+	GetHandleVerifier [0x0x7ff654f46bb0+79712]
+	(No symbol) [0x0x7ff654cdc0ea]
+	(No symbol) [0x0x7ff654d32f56]
+	(No symbol) [0x0x7ff654d3320c]
+	(No symbol) [0x0x7ff654d865b7]
+	(No symbol) [0x0x7ff654d5b17f]
+	(No symbol) [0x0x7ff654d833d0]
+	(No symbol) [0x0x7ff654d5af13]
+	(No symbol) [0x0x7ff654d24151]
+	(No symbol) [0x0x7ff654d24ee3]
+	GetHandleVerifier [0x0x7ff65520686d+2962461]
+	GetHandleVerifier [0x0x7ff655200b8d+2938685]
+	GetHandleVerifier [0x0x7ff65521f74d+3064573]
+	GetHandleVerifier [0x0x7ff654f60c9e+186446]
+	GetHandleVerifier [0x0x7ff654f68a6f+218655]
+	GetHandleVerifier [0x0x7ff654f4f944+115956]
+	GetHandleVerifier [0x0x7ff654f4faf9+116393]
+	GetHandleVerifier [0x0x7ff654f35f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1799,27 +1799,27 @@
       <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff654f46b55+79621]
+	GetHandleVerifier [0x0x7ff654f46bb0+79712]
+	(No symbol) [0x0x7ff654cdc0ea]
+	(No symbol) [0x0x7ff654d32f56]
+	(No symbol) [0x0x7ff654d3320c]
+	(No symbol) [0x0x7ff654d865b7]
+	(No symbol) [0x0x7ff654d5b17f]
+	(No symbol) [0x0x7ff654d833d0]
+	(No symbol) [0x0x7ff654d5af13]
+	(No symbol) [0x0x7ff654d24151]
+	(No symbol) [0x0x7ff654d24ee3]
+	GetHandleVerifier [0x0x7ff65520686d+2962461]
+	GetHandleVerifier [0x0x7ff655200b8d+2938685]
+	GetHandleVerifier [0x0x7ff65521f74d+3064573]
+	GetHandleVerifier [0x0x7ff654f60c9e+186446]
+	GetHandleVerifier [0x0x7ff654f68a6f+218655]
+	GetHandleVerifier [0x0x7ff654f4f944+115956]
+	GetHandleVerifier [0x0x7ff654f4faf9+116393]
+	GetHandleVerifier [0x0x7ff654f35f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1869,34 +1869,34 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>£34.90</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>£34.90</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>£34.90</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>£35.00</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>£34.95</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>£34.99</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>£34.99</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>£34.99</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>£35.00</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>£34.95</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>£34.99</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>£38.00</t>
@@ -1920,27 +1920,27 @@
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff654f46b55+79621]
+	GetHandleVerifier [0x0x7ff654f46bb0+79712]
+	(No symbol) [0x0x7ff654cdc0ea]
+	(No symbol) [0x0x7ff654d32f56]
+	(No symbol) [0x0x7ff654d3320c]
+	(No symbol) [0x0x7ff654d865b7]
+	(No symbol) [0x0x7ff654d5b17f]
+	(No symbol) [0x0x7ff654d833d0]
+	(No symbol) [0x0x7ff654d5af13]
+	(No symbol) [0x0x7ff654d24151]
+	(No symbol) [0x0x7ff654d24ee3]
+	GetHandleVerifier [0x0x7ff65520686d+2962461]
+	GetHandleVerifier [0x0x7ff655200b8d+2938685]
+	GetHandleVerifier [0x0x7ff65521f74d+3064573]
+	GetHandleVerifier [0x0x7ff654f60c9e+186446]
+	GetHandleVerifier [0x0x7ff654f68a6f+218655]
+	GetHandleVerifier [0x0x7ff654f4f944+115956]
+	GetHandleVerifier [0x0x7ff654f4faf9+116393]
+	GetHandleVerifier [0x0x7ff654f35f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2041,27 +2041,27 @@
       <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff654f46b55+79621]
+	GetHandleVerifier [0x0x7ff654f46bb0+79712]
+	(No symbol) [0x0x7ff654cdc0ea]
+	(No symbol) [0x0x7ff654d32f56]
+	(No symbol) [0x0x7ff654d3320c]
+	(No symbol) [0x0x7ff654d865b7]
+	(No symbol) [0x0x7ff654d5b17f]
+	(No symbol) [0x0x7ff654d833d0]
+	(No symbol) [0x0x7ff654d5af13]
+	(No symbol) [0x0x7ff654d24151]
+	(No symbol) [0x0x7ff654d24ee3]
+	GetHandleVerifier [0x0x7ff65520686d+2962461]
+	GetHandleVerifier [0x0x7ff655200b8d+2938685]
+	GetHandleVerifier [0x0x7ff65521f74d+3064573]
+	GetHandleVerifier [0x0x7ff654f60c9e+186446]
+	GetHandleVerifier [0x0x7ff654f68a6f+218655]
+	GetHandleVerifier [0x0x7ff654f4f944+115956]
+	GetHandleVerifier [0x0x7ff654f4faf9+116393]
+	GetHandleVerifier [0x0x7ff654f35f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2162,27 +2162,27 @@
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff654f46b55+79621]
+	GetHandleVerifier [0x0x7ff654f46bb0+79712]
+	(No symbol) [0x0x7ff654cdc0ea]
+	(No symbol) [0x0x7ff654d32f56]
+	(No symbol) [0x0x7ff654d3320c]
+	(No symbol) [0x0x7ff654d865b7]
+	(No symbol) [0x0x7ff654d5b17f]
+	(No symbol) [0x0x7ff654d833d0]
+	(No symbol) [0x0x7ff654d5af13]
+	(No symbol) [0x0x7ff654d24151]
+	(No symbol) [0x0x7ff654d24ee3]
+	GetHandleVerifier [0x0x7ff65520686d+2962461]
+	GetHandleVerifier [0x0x7ff655200b8d+2938685]
+	GetHandleVerifier [0x0x7ff65521f74d+3064573]
+	GetHandleVerifier [0x0x7ff654f60c9e+186446]
+	GetHandleVerifier [0x0x7ff654f68a6f+218655]
+	GetHandleVerifier [0x0x7ff654f4f944+115956]
+	GetHandleVerifier [0x0x7ff654f4faf9+116393]
+	GetHandleVerifier [0x0x7ff654f35f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2283,27 +2283,27 @@
       <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff654f46b55+79621]
+	GetHandleVerifier [0x0x7ff654f46bb0+79712]
+	(No symbol) [0x0x7ff654cdc0ea]
+	(No symbol) [0x0x7ff654d32f56]
+	(No symbol) [0x0x7ff654d3320c]
+	(No symbol) [0x0x7ff654d865b7]
+	(No symbol) [0x0x7ff654d5b17f]
+	(No symbol) [0x0x7ff654d833d0]
+	(No symbol) [0x0x7ff654d5af13]
+	(No symbol) [0x0x7ff654d24151]
+	(No symbol) [0x0x7ff654d24ee3]
+	GetHandleVerifier [0x0x7ff65520686d+2962461]
+	GetHandleVerifier [0x0x7ff655200b8d+2938685]
+	GetHandleVerifier [0x0x7ff65521f74d+3064573]
+	GetHandleVerifier [0x0x7ff654f60c9e+186446]
+	GetHandleVerifier [0x0x7ff654f68a6f+218655]
+	GetHandleVerifier [0x0x7ff654f4f944+115956]
+	GetHandleVerifier [0x0x7ff654f4faf9+116393]
+	GetHandleVerifier [0x0x7ff654f35f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2501,27 +2501,27 @@
       <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff654f46b55+79621]
+	GetHandleVerifier [0x0x7ff654f46bb0+79712]
+	(No symbol) [0x0x7ff654cdc0ea]
+	(No symbol) [0x0x7ff654d32f56]
+	(No symbol) [0x0x7ff654d3320c]
+	(No symbol) [0x0x7ff654d865b7]
+	(No symbol) [0x0x7ff654d5b17f]
+	(No symbol) [0x0x7ff654d833d0]
+	(No symbol) [0x0x7ff654d5af13]
+	(No symbol) [0x0x7ff654d24151]
+	(No symbol) [0x0x7ff654d24ee3]
+	GetHandleVerifier [0x0x7ff65520686d+2962461]
+	GetHandleVerifier [0x0x7ff655200b8d+2938685]
+	GetHandleVerifier [0x0x7ff65521f74d+3064573]
+	GetHandleVerifier [0x0x7ff654f60c9e+186446]
+	GetHandleVerifier [0x0x7ff654f68a6f+218655]
+	GetHandleVerifier [0x0x7ff654f4f944+115956]
+	GetHandleVerifier [0x0x7ff654f4faf9+116393]
+	GetHandleVerifier [0x0x7ff654f35f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2571,17 +2571,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>£30.98</t>
+          <t>£29.80</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>£30.98</t>
+          <t>£29.80</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>£30.98</t>
+          <t>£29.80</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2622,27 +2622,27 @@
       <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff654f46b55+79621]
+	GetHandleVerifier [0x0x7ff654f46bb0+79712]
+	(No symbol) [0x0x7ff654cdc0ea]
+	(No symbol) [0x0x7ff654d32f56]
+	(No symbol) [0x0x7ff654d3320c]
+	(No symbol) [0x0x7ff654d865b7]
+	(No symbol) [0x0x7ff654d5b17f]
+	(No symbol) [0x0x7ff654d833d0]
+	(No symbol) [0x0x7ff654d5af13]
+	(No symbol) [0x0x7ff654d24151]
+	(No symbol) [0x0x7ff654d24ee3]
+	GetHandleVerifier [0x0x7ff65520686d+2962461]
+	GetHandleVerifier [0x0x7ff655200b8d+2938685]
+	GetHandleVerifier [0x0x7ff65521f74d+3064573]
+	GetHandleVerifier [0x0x7ff654f60c9e+186446]
+	GetHandleVerifier [0x0x7ff654f68a6f+218655]
+	GetHandleVerifier [0x0x7ff654f4f944+115956]
+	GetHandleVerifier [0x0x7ff654f4faf9+116393]
+	GetHandleVerifier [0x0x7ff654f35f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2692,17 +2692,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>£37.49</t>
+          <t>£36.00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>£37.49</t>
+          <t>£36.00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>£37.49</t>
+          <t>£36.00</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2743,27 +2743,27 @@
       <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff654f46b55+79621]
+	GetHandleVerifier [0x0x7ff654f46bb0+79712]
+	(No symbol) [0x0x7ff654cdc0ea]
+	(No symbol) [0x0x7ff654d32f56]
+	(No symbol) [0x0x7ff654d3320c]
+	(No symbol) [0x0x7ff654d865b7]
+	(No symbol) [0x0x7ff654d5b17f]
+	(No symbol) [0x0x7ff654d833d0]
+	(No symbol) [0x0x7ff654d5af13]
+	(No symbol) [0x0x7ff654d24151]
+	(No symbol) [0x0x7ff654d24ee3]
+	GetHandleVerifier [0x0x7ff65520686d+2962461]
+	GetHandleVerifier [0x0x7ff655200b8d+2938685]
+	GetHandleVerifier [0x0x7ff65521f74d+3064573]
+	GetHandleVerifier [0x0x7ff654f60c9e+186446]
+	GetHandleVerifier [0x0x7ff654f68a6f+218655]
+	GetHandleVerifier [0x0x7ff654f4f944+115956]
+	GetHandleVerifier [0x0x7ff654f4faf9+116393]
+	GetHandleVerifier [0x0x7ff654f35f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2813,17 +2813,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>£40.49</t>
+          <t>£39.15</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>£40.49</t>
+          <t>£39.15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>£40.49</t>
+          <t>£39.15</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2864,27 +2864,27 @@
       <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff654f46b55+79621]
+	GetHandleVerifier [0x0x7ff654f46bb0+79712]
+	(No symbol) [0x0x7ff654cdc0ea]
+	(No symbol) [0x0x7ff654d32f56]
+	(No symbol) [0x0x7ff654d3320c]
+	(No symbol) [0x0x7ff654d865b7]
+	(No symbol) [0x0x7ff654d5b17f]
+	(No symbol) [0x0x7ff654d833d0]
+	(No symbol) [0x0x7ff654d5af13]
+	(No symbol) [0x0x7ff654d24151]
+	(No symbol) [0x0x7ff654d24ee3]
+	GetHandleVerifier [0x0x7ff65520686d+2962461]
+	GetHandleVerifier [0x0x7ff655200b8d+2938685]
+	GetHandleVerifier [0x0x7ff65521f74d+3064573]
+	GetHandleVerifier [0x0x7ff654f60c9e+186446]
+	GetHandleVerifier [0x0x7ff654f68a6f+218655]
+	GetHandleVerifier [0x0x7ff654f4f944+115956]
+	GetHandleVerifier [0x0x7ff654f4faf9+116393]
+	GetHandleVerifier [0x0x7ff654f35f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2934,17 +2934,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>£44.98</t>
+          <t>£43.62</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>£44.98</t>
+          <t>£43.62</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>£44.98</t>
+          <t>£43.62</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2985,27 +2985,27 @@
       <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff654f46b55+79621]
+	GetHandleVerifier [0x0x7ff654f46bb0+79712]
+	(No symbol) [0x0x7ff654cdc0ea]
+	(No symbol) [0x0x7ff654d32f56]
+	(No symbol) [0x0x7ff654d3320c]
+	(No symbol) [0x0x7ff654d865b7]
+	(No symbol) [0x0x7ff654d5b17f]
+	(No symbol) [0x0x7ff654d833d0]
+	(No symbol) [0x0x7ff654d5af13]
+	(No symbol) [0x0x7ff654d24151]
+	(No symbol) [0x0x7ff654d24ee3]
+	GetHandleVerifier [0x0x7ff65520686d+2962461]
+	GetHandleVerifier [0x0x7ff655200b8d+2938685]
+	GetHandleVerifier [0x0x7ff65521f74d+3064573]
+	GetHandleVerifier [0x0x7ff654f60c9e+186446]
+	GetHandleVerifier [0x0x7ff654f68a6f+218655]
+	GetHandleVerifier [0x0x7ff654f4f944+115956]
+	GetHandleVerifier [0x0x7ff654f4faf9+116393]
+	GetHandleVerifier [0x0x7ff654f35f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -3055,17 +3055,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>£45.49</t>
+          <t>£43.35</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>£45.49</t>
+          <t>£43.35</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>£45.49</t>
+          <t>£43.35</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3106,27 +3106,27 @@
       <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff654f46b55+79621]
+	GetHandleVerifier [0x0x7ff654f46bb0+79712]
+	(No symbol) [0x0x7ff654cdc0ea]
+	(No symbol) [0x0x7ff654d32f56]
+	(No symbol) [0x0x7ff654d3320c]
+	(No symbol) [0x0x7ff654d865b7]
+	(No symbol) [0x0x7ff654d5b17f]
+	(No symbol) [0x0x7ff654d833d0]
+	(No symbol) [0x0x7ff654d5af13]
+	(No symbol) [0x0x7ff654d24151]
+	(No symbol) [0x0x7ff654d24ee3]
+	GetHandleVerifier [0x0x7ff65520686d+2962461]
+	GetHandleVerifier [0x0x7ff655200b8d+2938685]
+	GetHandleVerifier [0x0x7ff65521f74d+3064573]
+	GetHandleVerifier [0x0x7ff654f60c9e+186446]
+	GetHandleVerifier [0x0x7ff654f68a6f+218655]
+	GetHandleVerifier [0x0x7ff654f4f944+115956]
+	GetHandleVerifier [0x0x7ff654f4faf9+116393]
+	GetHandleVerifier [0x0x7ff654f35f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -3176,17 +3176,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>£43.99</t>
+          <t>£43.95</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>£43.99</t>
+          <t>£43.95</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>£43.99</t>
+          <t>£43.95</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3227,27 +3227,27 @@
       <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff654f46b55+79621]
+	GetHandleVerifier [0x0x7ff654f46bb0+79712]
+	(No symbol) [0x0x7ff654cdc0ea]
+	(No symbol) [0x0x7ff654d32f56]
+	(No symbol) [0x0x7ff654d3320c]
+	(No symbol) [0x0x7ff654d865b7]
+	(No symbol) [0x0x7ff654d5b17f]
+	(No symbol) [0x0x7ff654d833d0]
+	(No symbol) [0x0x7ff654d5af13]
+	(No symbol) [0x0x7ff654d24151]
+	(No symbol) [0x0x7ff654d24ee3]
+	GetHandleVerifier [0x0x7ff65520686d+2962461]
+	GetHandleVerifier [0x0x7ff655200b8d+2938685]
+	GetHandleVerifier [0x0x7ff65521f74d+3064573]
+	GetHandleVerifier [0x0x7ff654f60c9e+186446]
+	GetHandleVerifier [0x0x7ff654f68a6f+218655]
+	GetHandleVerifier [0x0x7ff654f4f944+115956]
+	GetHandleVerifier [0x0x7ff654f4faf9+116393]
+	GetHandleVerifier [0x0x7ff654f35f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -3348,27 +3348,27 @@
       <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff654f46b55+79621]
+	GetHandleVerifier [0x0x7ff654f46bb0+79712]
+	(No symbol) [0x0x7ff654cdc0ea]
+	(No symbol) [0x0x7ff654d32f56]
+	(No symbol) [0x0x7ff654d3320c]
+	(No symbol) [0x0x7ff654d865b7]
+	(No symbol) [0x0x7ff654d5b17f]
+	(No symbol) [0x0x7ff654d833d0]
+	(No symbol) [0x0x7ff654d5af13]
+	(No symbol) [0x0x7ff654d24151]
+	(No symbol) [0x0x7ff654d24ee3]
+	GetHandleVerifier [0x0x7ff65520686d+2962461]
+	GetHandleVerifier [0x0x7ff655200b8d+2938685]
+	GetHandleVerifier [0x0x7ff65521f74d+3064573]
+	GetHandleVerifier [0x0x7ff654f60c9e+186446]
+	GetHandleVerifier [0x0x7ff654f68a6f+218655]
+	GetHandleVerifier [0x0x7ff654f4f944+115956]
+	GetHandleVerifier [0x0x7ff654f4faf9+116393]
+	GetHandleVerifier [0x0x7ff654f35f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -3418,17 +3418,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>£44.99</t>
+          <t>£44.00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>£44.99</t>
+          <t>£44.00</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>£44.99</t>
+          <t>£44.00</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3469,27 +3469,27 @@
       <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff654f46b55+79621]
+	GetHandleVerifier [0x0x7ff654f46bb0+79712]
+	(No symbol) [0x0x7ff654cdc0ea]
+	(No symbol) [0x0x7ff654d32f56]
+	(No symbol) [0x0x7ff654d3320c]
+	(No symbol) [0x0x7ff654d865b7]
+	(No symbol) [0x0x7ff654d5b17f]
+	(No symbol) [0x0x7ff654d833d0]
+	(No symbol) [0x0x7ff654d5af13]
+	(No symbol) [0x0x7ff654d24151]
+	(No symbol) [0x0x7ff654d24ee3]
+	GetHandleVerifier [0x0x7ff65520686d+2962461]
+	GetHandleVerifier [0x0x7ff655200b8d+2938685]
+	GetHandleVerifier [0x0x7ff65521f74d+3064573]
+	GetHandleVerifier [0x0x7ff654f60c9e+186446]
+	GetHandleVerifier [0x0x7ff654f68a6f+218655]
+	GetHandleVerifier [0x0x7ff654f4f944+115956]
+	GetHandleVerifier [0x0x7ff654f4faf9+116393]
+	GetHandleVerifier [0x0x7ff654f35f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -3539,17 +3539,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>£1,183.00</t>
+          <t>£1,160.00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>£1,183.00</t>
+          <t>£1,160.00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>£1,183.00</t>
+          <t>£1,160.00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_06-08-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_06-08-2025.xlsx
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff654f46b55+79621]
-	GetHandleVerifier [0x0x7ff654f46bb0+79712]
-	(No symbol) [0x0x7ff654cdc0ea]
-	(No symbol) [0x0x7ff654d32f56]
-	(No symbol) [0x0x7ff654d3320c]
-	(No symbol) [0x0x7ff654d865b7]
-	(No symbol) [0x0x7ff654d5b17f]
-	(No symbol) [0x0x7ff654d833d0]
-	(No symbol) [0x0x7ff654d5af13]
-	(No symbol) [0x0x7ff654d24151]
-	(No symbol) [0x0x7ff654d24ee3]
-	GetHandleVerifier [0x0x7ff65520686d+2962461]
-	GetHandleVerifier [0x0x7ff655200b8d+2938685]
-	GetHandleVerifier [0x0x7ff65521f74d+3064573]
-	GetHandleVerifier [0x0x7ff654f60c9e+186446]
-	GetHandleVerifier [0x0x7ff654f68a6f+218655]
-	GetHandleVerifier [0x0x7ff654f4f944+115956]
-	GetHandleVerifier [0x0x7ff654f4faf9+116393]
-	GetHandleVerifier [0x0x7ff654f35f28+10968]
+	GetHandleVerifier [0x0x7ff76d756b55+79621]
+	GetHandleVerifier [0x0x7ff76d756bb0+79712]
+	(No symbol) [0x0x7ff76d4ec0ea]
+	(No symbol) [0x0x7ff76d542f56]
+	(No symbol) [0x0x7ff76d54320c]
+	(No symbol) [0x0x7ff76d5965b7]
+	(No symbol) [0x0x7ff76d56b17f]
+	(No symbol) [0x0x7ff76d5933d0]
+	(No symbol) [0x0x7ff76d56af13]
+	(No symbol) [0x0x7ff76d534151]
+	(No symbol) [0x0x7ff76d534ee3]
+	GetHandleVerifier [0x0x7ff76da1686d+2962461]
+	GetHandleVerifier [0x0x7ff76da10b8d+2938685]
+	GetHandleVerifier [0x0x7ff76da2f74d+3064573]
+	GetHandleVerifier [0x0x7ff76d770c9e+186446]
+	GetHandleVerifier [0x0x7ff76d778a6f+218655]
+	GetHandleVerifier [0x0x7ff76d75f944+115956]
+	GetHandleVerifier [0x0x7ff76d75faf9+116393]
+	GetHandleVerifier [0x0x7ff76d745f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -704,7 +704,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>£12.62</t>
+          <t>£12.13</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff654f46b55+79621]
-	GetHandleVerifier [0x0x7ff654f46bb0+79712]
-	(No symbol) [0x0x7ff654cdc0ea]
-	(No symbol) [0x0x7ff654d32f56]
-	(No symbol) [0x0x7ff654d3320c]
-	(No symbol) [0x0x7ff654d865b7]
-	(No symbol) [0x0x7ff654d5b17f]
-	(No symbol) [0x0x7ff654d833d0]
-	(No symbol) [0x0x7ff654d5af13]
-	(No symbol) [0x0x7ff654d24151]
-	(No symbol) [0x0x7ff654d24ee3]
-	GetHandleVerifier [0x0x7ff65520686d+2962461]
-	GetHandleVerifier [0x0x7ff655200b8d+2938685]
-	GetHandleVerifier [0x0x7ff65521f74d+3064573]
-	GetHandleVerifier [0x0x7ff654f60c9e+186446]
-	GetHandleVerifier [0x0x7ff654f68a6f+218655]
-	GetHandleVerifier [0x0x7ff654f4f944+115956]
-	GetHandleVerifier [0x0x7ff654f4faf9+116393]
-	GetHandleVerifier [0x0x7ff654f35f28+10968]
+	GetHandleVerifier [0x0x7ff76d756b55+79621]
+	GetHandleVerifier [0x0x7ff76d756bb0+79712]
+	(No symbol) [0x0x7ff76d4ec0ea]
+	(No symbol) [0x0x7ff76d542f56]
+	(No symbol) [0x0x7ff76d54320c]
+	(No symbol) [0x0x7ff76d5965b7]
+	(No symbol) [0x0x7ff76d56b17f]
+	(No symbol) [0x0x7ff76d5933d0]
+	(No symbol) [0x0x7ff76d56af13]
+	(No symbol) [0x0x7ff76d534151]
+	(No symbol) [0x0x7ff76d534ee3]
+	GetHandleVerifier [0x0x7ff76da1686d+2962461]
+	GetHandleVerifier [0x0x7ff76da10b8d+2938685]
+	GetHandleVerifier [0x0x7ff76da2f74d+3064573]
+	GetHandleVerifier [0x0x7ff76d770c9e+186446]
+	GetHandleVerifier [0x0x7ff76d778a6f+218655]
+	GetHandleVerifier [0x0x7ff76d75f944+115956]
+	GetHandleVerifier [0x0x7ff76d75faf9+116393]
+	GetHandleVerifier [0x0x7ff76d745f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -825,7 +825,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>£16.18</t>
+          <t>£15.75</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff654f46b55+79621]
-	GetHandleVerifier [0x0x7ff654f46bb0+79712]
-	(No symbol) [0x0x7ff654cdc0ea]
-	(No symbol) [0x0x7ff654d32f56]
-	(No symbol) [0x0x7ff654d3320c]
-	(No symbol) [0x0x7ff654d865b7]
-	(No symbol) [0x0x7ff654d5b17f]
-	(No symbol) [0x0x7ff654d833d0]
-	(No symbol) [0x0x7ff654d5af13]
-	(No symbol) [0x0x7ff654d24151]
-	(No symbol) [0x0x7ff654d24ee3]
-	GetHandleVerifier [0x0x7ff65520686d+2962461]
-	GetHandleVerifier [0x0x7ff655200b8d+2938685]
-	GetHandleVerifier [0x0x7ff65521f74d+3064573]
-	GetHandleVerifier [0x0x7ff654f60c9e+186446]
-	GetHandleVerifier [0x0x7ff654f68a6f+218655]
-	GetHandleVerifier [0x0x7ff654f4f944+115956]
-	GetHandleVerifier [0x0x7ff654f4faf9+116393]
-	GetHandleVerifier [0x0x7ff654f35f28+10968]
+	GetHandleVerifier [0x0x7ff76d756b55+79621]
+	GetHandleVerifier [0x0x7ff76d756bb0+79712]
+	(No symbol) [0x0x7ff76d4ec0ea]
+	(No symbol) [0x0x7ff76d542f56]
+	(No symbol) [0x0x7ff76d54320c]
+	(No symbol) [0x0x7ff76d5965b7]
+	(No symbol) [0x0x7ff76d56b17f]
+	(No symbol) [0x0x7ff76d5933d0]
+	(No symbol) [0x0x7ff76d56af13]
+	(No symbol) [0x0x7ff76d534151]
+	(No symbol) [0x0x7ff76d534ee3]
+	GetHandleVerifier [0x0x7ff76da1686d+2962461]
+	GetHandleVerifier [0x0x7ff76da10b8d+2938685]
+	GetHandleVerifier [0x0x7ff76da2f74d+3064573]
+	GetHandleVerifier [0x0x7ff76d770c9e+186446]
+	GetHandleVerifier [0x0x7ff76d778a6f+218655]
+	GetHandleVerifier [0x0x7ff76d75f944+115956]
+	GetHandleVerifier [0x0x7ff76d75faf9+116393]
+	GetHandleVerifier [0x0x7ff76d745f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -901,34 +901,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>£16.50</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>£16.50</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>£16.50</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>£16.65</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>£16.60</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>£16.50</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>£16.50</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>£16.65</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>£16.60</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>£16.60</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>£17.48</t>
@@ -946,7 +946,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>£16.46</t>
+          <t>£15.91</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff654f46b55+79621]
-	GetHandleVerifier [0x0x7ff654f46bb0+79712]
-	(No symbol) [0x0x7ff654cdc0ea]
-	(No symbol) [0x0x7ff654d32f56]
-	(No symbol) [0x0x7ff654d3320c]
-	(No symbol) [0x0x7ff654d865b7]
-	(No symbol) [0x0x7ff654d5b17f]
-	(No symbol) [0x0x7ff654d833d0]
-	(No symbol) [0x0x7ff654d5af13]
-	(No symbol) [0x0x7ff654d24151]
-	(No symbol) [0x0x7ff654d24ee3]
-	GetHandleVerifier [0x0x7ff65520686d+2962461]
-	GetHandleVerifier [0x0x7ff655200b8d+2938685]
-	GetHandleVerifier [0x0x7ff65521f74d+3064573]
-	GetHandleVerifier [0x0x7ff654f60c9e+186446]
-	GetHandleVerifier [0x0x7ff654f68a6f+218655]
-	GetHandleVerifier [0x0x7ff654f4f944+115956]
-	GetHandleVerifier [0x0x7ff654f4faf9+116393]
-	GetHandleVerifier [0x0x7ff654f35f28+10968]
+	GetHandleVerifier [0x0x7ff76d756b55+79621]
+	GetHandleVerifier [0x0x7ff76d756bb0+79712]
+	(No symbol) [0x0x7ff76d4ec0ea]
+	(No symbol) [0x0x7ff76d542f56]
+	(No symbol) [0x0x7ff76d54320c]
+	(No symbol) [0x0x7ff76d5965b7]
+	(No symbol) [0x0x7ff76d56b17f]
+	(No symbol) [0x0x7ff76d5933d0]
+	(No symbol) [0x0x7ff76d56af13]
+	(No symbol) [0x0x7ff76d534151]
+	(No symbol) [0x0x7ff76d534ee3]
+	GetHandleVerifier [0x0x7ff76da1686d+2962461]
+	GetHandleVerifier [0x0x7ff76da10b8d+2938685]
+	GetHandleVerifier [0x0x7ff76da2f74d+3064573]
+	GetHandleVerifier [0x0x7ff76d770c9e+186446]
+	GetHandleVerifier [0x0x7ff76d778a6f+218655]
+	GetHandleVerifier [0x0x7ff76d75f944+115956]
+	GetHandleVerifier [0x0x7ff76d75faf9+116393]
+	GetHandleVerifier [0x0x7ff76d745f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>£21.08</t>
+          <t>£20.60</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff654f46b55+79621]
-	GetHandleVerifier [0x0x7ff654f46bb0+79712]
-	(No symbol) [0x0x7ff654cdc0ea]
-	(No symbol) [0x0x7ff654d32f56]
-	(No symbol) [0x0x7ff654d3320c]
-	(No symbol) [0x0x7ff654d865b7]
-	(No symbol) [0x0x7ff654d5b17f]
-	(No symbol) [0x0x7ff654d833d0]
-	(No symbol) [0x0x7ff654d5af13]
-	(No symbol) [0x0x7ff654d24151]
-	(No symbol) [0x0x7ff654d24ee3]
-	GetHandleVerifier [0x0x7ff65520686d+2962461]
-	GetHandleVerifier [0x0x7ff655200b8d+2938685]
-	GetHandleVerifier [0x0x7ff65521f74d+3064573]
-	GetHandleVerifier [0x0x7ff654f60c9e+186446]
-	GetHandleVerifier [0x0x7ff654f68a6f+218655]
-	GetHandleVerifier [0x0x7ff654f4f944+115956]
-	GetHandleVerifier [0x0x7ff654f4faf9+116393]
-	GetHandleVerifier [0x0x7ff654f35f28+10968]
+	GetHandleVerifier [0x0x7ff76d756b55+79621]
+	GetHandleVerifier [0x0x7ff76d756bb0+79712]
+	(No symbol) [0x0x7ff76d4ec0ea]
+	(No symbol) [0x0x7ff76d542f56]
+	(No symbol) [0x0x7ff76d54320c]
+	(No symbol) [0x0x7ff76d5965b7]
+	(No symbol) [0x0x7ff76d56b17f]
+	(No symbol) [0x0x7ff76d5933d0]
+	(No symbol) [0x0x7ff76d56af13]
+	(No symbol) [0x0x7ff76d534151]
+	(No symbol) [0x0x7ff76d534ee3]
+	GetHandleVerifier [0x0x7ff76da1686d+2962461]
+	GetHandleVerifier [0x0x7ff76da10b8d+2938685]
+	GetHandleVerifier [0x0x7ff76da2f74d+3064573]
+	GetHandleVerifier [0x0x7ff76d770c9e+186446]
+	GetHandleVerifier [0x0x7ff76d778a6f+218655]
+	GetHandleVerifier [0x0x7ff76d75f944+115956]
+	GetHandleVerifier [0x0x7ff76d75faf9+116393]
+	GetHandleVerifier [0x0x7ff76d745f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>£22.76</t>
+          <t>£22.24</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff654f46b55+79621]
-	GetHandleVerifier [0x0x7ff654f46bb0+79712]
-	(No symbol) [0x0x7ff654cdc0ea]
-	(No symbol) [0x0x7ff654d32f56]
-	(No symbol) [0x0x7ff654d3320c]
-	(No symbol) [0x0x7ff654d865b7]
-	(No symbol) [0x0x7ff654d5b17f]
-	(No symbol) [0x0x7ff654d833d0]
-	(No symbol) [0x0x7ff654d5af13]
-	(No symbol) [0x0x7ff654d24151]
-	(No symbol) [0x0x7ff654d24ee3]
-	GetHandleVerifier [0x0x7ff65520686d+2962461]
-	GetHandleVerifier [0x0x7ff655200b8d+2938685]
-	GetHandleVerifier [0x0x7ff65521f74d+3064573]
-	GetHandleVerifier [0x0x7ff654f60c9e+186446]
-	GetHandleVerifier [0x0x7ff654f68a6f+218655]
-	GetHandleVerifier [0x0x7ff654f4f944+115956]
-	GetHandleVerifier [0x0x7ff654f4faf9+116393]
-	GetHandleVerifier [0x0x7ff654f35f28+10968]
+	GetHandleVerifier [0x0x7ff76d756b55+79621]
+	GetHandleVerifier [0x0x7ff76d756bb0+79712]
+	(No symbol) [0x0x7ff76d4ec0ea]
+	(No symbol) [0x0x7ff76d542f56]
+	(No symbol) [0x0x7ff76d54320c]
+	(No symbol) [0x0x7ff76d5965b7]
+	(No symbol) [0x0x7ff76d56b17f]
+	(No symbol) [0x0x7ff76d5933d0]
+	(No symbol) [0x0x7ff76d56af13]
+	(No symbol) [0x0x7ff76d534151]
+	(No symbol) [0x0x7ff76d534ee3]
+	GetHandleVerifier [0x0x7ff76da1686d+2962461]
+	GetHandleVerifier [0x0x7ff76da10b8d+2938685]
+	GetHandleVerifier [0x0x7ff76da2f74d+3064573]
+	GetHandleVerifier [0x0x7ff76d770c9e+186446]
+	GetHandleVerifier [0x0x7ff76d778a6f+218655]
+	GetHandleVerifier [0x0x7ff76d75f944+115956]
+	GetHandleVerifier [0x0x7ff76d75faf9+116393]
+	GetHandleVerifier [0x0x7ff76d745f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>£23.09</t>
+          <t>£22.57</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff654f46b55+79621]
-	GetHandleVerifier [0x0x7ff654f46bb0+79712]
-	(No symbol) [0x0x7ff654cdc0ea]
-	(No symbol) [0x0x7ff654d32f56]
-	(No symbol) [0x0x7ff654d3320c]
-	(No symbol) [0x0x7ff654d865b7]
-	(No symbol) [0x0x7ff654d5b17f]
-	(No symbol) [0x0x7ff654d833d0]
-	(No symbol) [0x0x7ff654d5af13]
-	(No symbol) [0x0x7ff654d24151]
-	(No symbol) [0x0x7ff654d24ee3]
-	GetHandleVerifier [0x0x7ff65520686d+2962461]
-	GetHandleVerifier [0x0x7ff655200b8d+2938685]
-	GetHandleVerifier [0x0x7ff65521f74d+3064573]
-	GetHandleVerifier [0x0x7ff654f60c9e+186446]
-	GetHandleVerifier [0x0x7ff654f68a6f+218655]
-	GetHandleVerifier [0x0x7ff654f4f944+115956]
-	GetHandleVerifier [0x0x7ff654f4faf9+116393]
-	GetHandleVerifier [0x0x7ff654f35f28+10968]
+	GetHandleVerifier [0x0x7ff76d756b55+79621]
+	GetHandleVerifier [0x0x7ff76d756bb0+79712]
+	(No symbol) [0x0x7ff76d4ec0ea]
+	(No symbol) [0x0x7ff76d542f56]
+	(No symbol) [0x0x7ff76d54320c]
+	(No symbol) [0x0x7ff76d5965b7]
+	(No symbol) [0x0x7ff76d56b17f]
+	(No symbol) [0x0x7ff76d5933d0]
+	(No symbol) [0x0x7ff76d56af13]
+	(No symbol) [0x0x7ff76d534151]
+	(No symbol) [0x0x7ff76d534ee3]
+	GetHandleVerifier [0x0x7ff76da1686d+2962461]
+	GetHandleVerifier [0x0x7ff76da10b8d+2938685]
+	GetHandleVerifier [0x0x7ff76da2f74d+3064573]
+	GetHandleVerifier [0x0x7ff76d770c9e+186446]
+	GetHandleVerifier [0x0x7ff76d778a6f+218655]
+	GetHandleVerifier [0x0x7ff76d75f944+115956]
+	GetHandleVerifier [0x0x7ff76d75faf9+116393]
+	GetHandleVerifier [0x0x7ff76d745f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>£26.33</t>
+          <t>£25.79</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff654f46b55+79621]
-	GetHandleVerifier [0x0x7ff654f46bb0+79712]
-	(No symbol) [0x0x7ff654cdc0ea]
-	(No symbol) [0x0x7ff654d32f56]
-	(No symbol) [0x0x7ff654d3320c]
-	(No symbol) [0x0x7ff654d865b7]
-	(No symbol) [0x0x7ff654d5b17f]
-	(No symbol) [0x0x7ff654d833d0]
-	(No symbol) [0x0x7ff654d5af13]
-	(No symbol) [0x0x7ff654d24151]
-	(No symbol) [0x0x7ff654d24ee3]
-	GetHandleVerifier [0x0x7ff65520686d+2962461]
-	GetHandleVerifier [0x0x7ff655200b8d+2938685]
-	GetHandleVerifier [0x0x7ff65521f74d+3064573]
-	GetHandleVerifier [0x0x7ff654f60c9e+186446]
-	GetHandleVerifier [0x0x7ff654f68a6f+218655]
-	GetHandleVerifier [0x0x7ff654f4f944+115956]
-	GetHandleVerifier [0x0x7ff654f4faf9+116393]
-	GetHandleVerifier [0x0x7ff654f35f28+10968]
+	GetHandleVerifier [0x0x7ff76d756b55+79621]
+	GetHandleVerifier [0x0x7ff76d756bb0+79712]
+	(No symbol) [0x0x7ff76d4ec0ea]
+	(No symbol) [0x0x7ff76d542f56]
+	(No symbol) [0x0x7ff76d54320c]
+	(No symbol) [0x0x7ff76d5965b7]
+	(No symbol) [0x0x7ff76d56b17f]
+	(No symbol) [0x0x7ff76d5933d0]
+	(No symbol) [0x0x7ff76d56af13]
+	(No symbol) [0x0x7ff76d534151]
+	(No symbol) [0x0x7ff76d534ee3]
+	GetHandleVerifier [0x0x7ff76da1686d+2962461]
+	GetHandleVerifier [0x0x7ff76da10b8d+2938685]
+	GetHandleVerifier [0x0x7ff76da2f74d+3064573]
+	GetHandleVerifier [0x0x7ff76d770c9e+186446]
+	GetHandleVerifier [0x0x7ff76d778a6f+218655]
+	GetHandleVerifier [0x0x7ff76d75f944+115956]
+	GetHandleVerifier [0x0x7ff76d75faf9+116393]
+	GetHandleVerifier [0x0x7ff76d745f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>£28.82</t>
+          <t>£27.95</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff654f46b55+79621]
-	GetHandleVerifier [0x0x7ff654f46bb0+79712]
-	(No symbol) [0x0x7ff654cdc0ea]
-	(No symbol) [0x0x7ff654d32f56]
-	(No symbol) [0x0x7ff654d3320c]
-	(No symbol) [0x0x7ff654d865b7]
-	(No symbol) [0x0x7ff654d5b17f]
-	(No symbol) [0x0x7ff654d833d0]
-	(No symbol) [0x0x7ff654d5af13]
-	(No symbol) [0x0x7ff654d24151]
-	(No symbol) [0x0x7ff654d24ee3]
-	GetHandleVerifier [0x0x7ff65520686d+2962461]
-	GetHandleVerifier [0x0x7ff655200b8d+2938685]
-	GetHandleVerifier [0x0x7ff65521f74d+3064573]
-	GetHandleVerifier [0x0x7ff654f60c9e+186446]
-	GetHandleVerifier [0x0x7ff654f68a6f+218655]
-	GetHandleVerifier [0x0x7ff654f4f944+115956]
-	GetHandleVerifier [0x0x7ff654f4faf9+116393]
-	GetHandleVerifier [0x0x7ff654f35f28+10968]
+	GetHandleVerifier [0x0x7ff76d756b55+79621]
+	GetHandleVerifier [0x0x7ff76d756bb0+79712]
+	(No symbol) [0x0x7ff76d4ec0ea]
+	(No symbol) [0x0x7ff76d542f56]
+	(No symbol) [0x0x7ff76d54320c]
+	(No symbol) [0x0x7ff76d5965b7]
+	(No symbol) [0x0x7ff76d56b17f]
+	(No symbol) [0x0x7ff76d5933d0]
+	(No symbol) [0x0x7ff76d56af13]
+	(No symbol) [0x0x7ff76d534151]
+	(No symbol) [0x0x7ff76d534ee3]
+	GetHandleVerifier [0x0x7ff76da1686d+2962461]
+	GetHandleVerifier [0x0x7ff76da10b8d+2938685]
+	GetHandleVerifier [0x0x7ff76da2f74d+3064573]
+	GetHandleVerifier [0x0x7ff76d770c9e+186446]
+	GetHandleVerifier [0x0x7ff76d778a6f+218655]
+	GetHandleVerifier [0x0x7ff76d75f944+115956]
+	GetHandleVerifier [0x0x7ff76d75faf9+116393]
+	GetHandleVerifier [0x0x7ff76d745f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>£28.12</t>
+          <t>£27.45</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff654f46b55+79621]
-	GetHandleVerifier [0x0x7ff654f46bb0+79712]
-	(No symbol) [0x0x7ff654cdc0ea]
-	(No symbol) [0x0x7ff654d32f56]
-	(No symbol) [0x0x7ff654d3320c]
-	(No symbol) [0x0x7ff654d865b7]
-	(No symbol) [0x0x7ff654d5b17f]
-	(No symbol) [0x0x7ff654d833d0]
-	(No symbol) [0x0x7ff654d5af13]
-	(No symbol) [0x0x7ff654d24151]
-	(No symbol) [0x0x7ff654d24ee3]
-	GetHandleVerifier [0x0x7ff65520686d+2962461]
-	GetHandleVerifier [0x0x7ff655200b8d+2938685]
-	GetHandleVerifier [0x0x7ff65521f74d+3064573]
-	GetHandleVerifier [0x0x7ff654f60c9e+186446]
-	GetHandleVerifier [0x0x7ff654f68a6f+218655]
-	GetHandleVerifier [0x0x7ff654f4f944+115956]
-	GetHandleVerifier [0x0x7ff654f4faf9+116393]
-	GetHandleVerifier [0x0x7ff654f35f28+10968]
+	GetHandleVerifier [0x0x7ff76d756b55+79621]
+	GetHandleVerifier [0x0x7ff76d756bb0+79712]
+	(No symbol) [0x0x7ff76d4ec0ea]
+	(No symbol) [0x0x7ff76d542f56]
+	(No symbol) [0x0x7ff76d54320c]
+	(No symbol) [0x0x7ff76d5965b7]
+	(No symbol) [0x0x7ff76d56b17f]
+	(No symbol) [0x0x7ff76d5933d0]
+	(No symbol) [0x0x7ff76d56af13]
+	(No symbol) [0x0x7ff76d534151]
+	(No symbol) [0x0x7ff76d534ee3]
+	GetHandleVerifier [0x0x7ff76da1686d+2962461]
+	GetHandleVerifier [0x0x7ff76da10b8d+2938685]
+	GetHandleVerifier [0x0x7ff76da2f74d+3064573]
+	GetHandleVerifier [0x0x7ff76d770c9e+186446]
+	GetHandleVerifier [0x0x7ff76d778a6f+218655]
+	GetHandleVerifier [0x0x7ff76d75f944+115956]
+	GetHandleVerifier [0x0x7ff76d75faf9+116393]
+	GetHandleVerifier [0x0x7ff76d745f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff654f46b55+79621]
-	GetHandleVerifier [0x0x7ff654f46bb0+79712]
-	(No symbol) [0x0x7ff654cdc0ea]
-	(No symbol) [0x0x7ff654d32f56]
-	(No symbol) [0x0x7ff654d3320c]
-	(No symbol) [0x0x7ff654d865b7]
-	(No symbol) [0x0x7ff654d5b17f]
-	(No symbol) [0x0x7ff654d833d0]
-	(No symbol) [0x0x7ff654d5af13]
-	(No symbol) [0x0x7ff654d24151]
-	(No symbol) [0x0x7ff654d24ee3]
-	GetHandleVerifier [0x0x7ff65520686d+2962461]
-	GetHandleVerifier [0x0x7ff655200b8d+2938685]
-	GetHandleVerifier [0x0x7ff65521f74d+3064573]
-	GetHandleVerifier [0x0x7ff654f60c9e+186446]
-	GetHandleVerifier [0x0x7ff654f68a6f+218655]
-	GetHandleVerifier [0x0x7ff654f4f944+115956]
-	GetHandleVerifier [0x0x7ff654f4faf9+116393]
-	GetHandleVerifier [0x0x7ff654f35f28+10968]
+	GetHandleVerifier [0x0x7ff76d756b55+79621]
+	GetHandleVerifier [0x0x7ff76d756bb0+79712]
+	(No symbol) [0x0x7ff76d4ec0ea]
+	(No symbol) [0x0x7ff76d542f56]
+	(No symbol) [0x0x7ff76d54320c]
+	(No symbol) [0x0x7ff76d5965b7]
+	(No symbol) [0x0x7ff76d56b17f]
+	(No symbol) [0x0x7ff76d5933d0]
+	(No symbol) [0x0x7ff76d56af13]
+	(No symbol) [0x0x7ff76d534151]
+	(No symbol) [0x0x7ff76d534ee3]
+	GetHandleVerifier [0x0x7ff76da1686d+2962461]
+	GetHandleVerifier [0x0x7ff76da10b8d+2938685]
+	GetHandleVerifier [0x0x7ff76da2f74d+3064573]
+	GetHandleVerifier [0x0x7ff76d770c9e+186446]
+	GetHandleVerifier [0x0x7ff76d778a6f+218655]
+	GetHandleVerifier [0x0x7ff76d75f944+115956]
+	GetHandleVerifier [0x0x7ff76d75faf9+116393]
+	GetHandleVerifier [0x0x7ff76d745f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>£34.48</t>
+          <t>£33.72</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff654f46b55+79621]
-	GetHandleVerifier [0x0x7ff654f46bb0+79712]
-	(No symbol) [0x0x7ff654cdc0ea]
-	(No symbol) [0x0x7ff654d32f56]
-	(No symbol) [0x0x7ff654d3320c]
-	(No symbol) [0x0x7ff654d865b7]
-	(No symbol) [0x0x7ff654d5b17f]
-	(No symbol) [0x0x7ff654d833d0]
-	(No symbol) [0x0x7ff654d5af13]
-	(No symbol) [0x0x7ff654d24151]
-	(No symbol) [0x0x7ff654d24ee3]
-	GetHandleVerifier [0x0x7ff65520686d+2962461]
-	GetHandleVerifier [0x0x7ff655200b8d+2938685]
-	GetHandleVerifier [0x0x7ff65521f74d+3064573]
-	GetHandleVerifier [0x0x7ff654f60c9e+186446]
-	GetHandleVerifier [0x0x7ff654f68a6f+218655]
-	GetHandleVerifier [0x0x7ff654f4f944+115956]
-	GetHandleVerifier [0x0x7ff654f4faf9+116393]
-	GetHandleVerifier [0x0x7ff654f35f28+10968]
+	GetHandleVerifier [0x0x7ff76d756b55+79621]
+	GetHandleVerifier [0x0x7ff76d756bb0+79712]
+	(No symbol) [0x0x7ff76d4ec0ea]
+	(No symbol) [0x0x7ff76d542f56]
+	(No symbol) [0x0x7ff76d54320c]
+	(No symbol) [0x0x7ff76d5965b7]
+	(No symbol) [0x0x7ff76d56b17f]
+	(No symbol) [0x0x7ff76d5933d0]
+	(No symbol) [0x0x7ff76d56af13]
+	(No symbol) [0x0x7ff76d534151]
+	(No symbol) [0x0x7ff76d534ee3]
+	GetHandleVerifier [0x0x7ff76da1686d+2962461]
+	GetHandleVerifier [0x0x7ff76da10b8d+2938685]
+	GetHandleVerifier [0x0x7ff76da2f74d+3064573]
+	GetHandleVerifier [0x0x7ff76d770c9e+186446]
+	GetHandleVerifier [0x0x7ff76d778a6f+218655]
+	GetHandleVerifier [0x0x7ff76d75f944+115956]
+	GetHandleVerifier [0x0x7ff76d75faf9+116393]
+	GetHandleVerifier [0x0x7ff76d745f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>£42.06</t>
+          <t>£41.10</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff654f46b55+79621]
-	GetHandleVerifier [0x0x7ff654f46bb0+79712]
-	(No symbol) [0x0x7ff654cdc0ea]
-	(No symbol) [0x0x7ff654d32f56]
-	(No symbol) [0x0x7ff654d3320c]
-	(No symbol) [0x0x7ff654d865b7]
-	(No symbol) [0x0x7ff654d5b17f]
-	(No symbol) [0x0x7ff654d833d0]
-	(No symbol) [0x0x7ff654d5af13]
-	(No symbol) [0x0x7ff654d24151]
-	(No symbol) [0x0x7ff654d24ee3]
-	GetHandleVerifier [0x0x7ff65520686d+2962461]
-	GetHandleVerifier [0x0x7ff655200b8d+2938685]
-	GetHandleVerifier [0x0x7ff65521f74d+3064573]
-	GetHandleVerifier [0x0x7ff654f60c9e+186446]
-	GetHandleVerifier [0x0x7ff654f68a6f+218655]
-	GetHandleVerifier [0x0x7ff654f4f944+115956]
-	GetHandleVerifier [0x0x7ff654f4faf9+116393]
-	GetHandleVerifier [0x0x7ff654f35f28+10968]
+	GetHandleVerifier [0x0x7ff76d756b55+79621]
+	GetHandleVerifier [0x0x7ff76d756bb0+79712]
+	(No symbol) [0x0x7ff76d4ec0ea]
+	(No symbol) [0x0x7ff76d542f56]
+	(No symbol) [0x0x7ff76d54320c]
+	(No symbol) [0x0x7ff76d5965b7]
+	(No symbol) [0x0x7ff76d56b17f]
+	(No symbol) [0x0x7ff76d5933d0]
+	(No symbol) [0x0x7ff76d56af13]
+	(No symbol) [0x0x7ff76d534151]
+	(No symbol) [0x0x7ff76d534ee3]
+	GetHandleVerifier [0x0x7ff76da1686d+2962461]
+	GetHandleVerifier [0x0x7ff76da10b8d+2938685]
+	GetHandleVerifier [0x0x7ff76da2f74d+3064573]
+	GetHandleVerifier [0x0x7ff76d770c9e+186446]
+	GetHandleVerifier [0x0x7ff76d778a6f+218655]
+	GetHandleVerifier [0x0x7ff76d75f944+115956]
+	GetHandleVerifier [0x0x7ff76d75faf9+116393]
+	GetHandleVerifier [0x0x7ff76d745f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>£43.04</t>
+          <t>£41.93</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff654f46b55+79621]
-	GetHandleVerifier [0x0x7ff654f46bb0+79712]
-	(No symbol) [0x0x7ff654cdc0ea]
-	(No symbol) [0x0x7ff654d32f56]
-	(No symbol) [0x0x7ff654d3320c]
-	(No symbol) [0x0x7ff654d865b7]
-	(No symbol) [0x0x7ff654d5b17f]
-	(No symbol) [0x0x7ff654d833d0]
-	(No symbol) [0x0x7ff654d5af13]
-	(No symbol) [0x0x7ff654d24151]
-	(No symbol) [0x0x7ff654d24ee3]
-	GetHandleVerifier [0x0x7ff65520686d+2962461]
-	GetHandleVerifier [0x0x7ff655200b8d+2938685]
-	GetHandleVerifier [0x0x7ff65521f74d+3064573]
-	GetHandleVerifier [0x0x7ff654f60c9e+186446]
-	GetHandleVerifier [0x0x7ff654f68a6f+218655]
-	GetHandleVerifier [0x0x7ff654f4f944+115956]
-	GetHandleVerifier [0x0x7ff654f4faf9+116393]
-	GetHandleVerifier [0x0x7ff654f35f28+10968]
+	GetHandleVerifier [0x0x7ff76d756b55+79621]
+	GetHandleVerifier [0x0x7ff76d756bb0+79712]
+	(No symbol) [0x0x7ff76d4ec0ea]
+	(No symbol) [0x0x7ff76d542f56]
+	(No symbol) [0x0x7ff76d54320c]
+	(No symbol) [0x0x7ff76d5965b7]
+	(No symbol) [0x0x7ff76d56b17f]
+	(No symbol) [0x0x7ff76d5933d0]
+	(No symbol) [0x0x7ff76d56af13]
+	(No symbol) [0x0x7ff76d534151]
+	(No symbol) [0x0x7ff76d534ee3]
+	GetHandleVerifier [0x0x7ff76da1686d+2962461]
+	GetHandleVerifier [0x0x7ff76da10b8d+2938685]
+	GetHandleVerifier [0x0x7ff76da2f74d+3064573]
+	GetHandleVerifier [0x0x7ff76d770c9e+186446]
+	GetHandleVerifier [0x0x7ff76d778a6f+218655]
+	GetHandleVerifier [0x0x7ff76d75f944+115956]
+	GetHandleVerifier [0x0x7ff76d75faf9+116393]
+	GetHandleVerifier [0x0x7ff76d745f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>£42.83</t>
+          <t>£41.86</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff654f46b55+79621]
-	GetHandleVerifier [0x0x7ff654f46bb0+79712]
-	(No symbol) [0x0x7ff654cdc0ea]
-	(No symbol) [0x0x7ff654d32f56]
-	(No symbol) [0x0x7ff654d3320c]
-	(No symbol) [0x0x7ff654d865b7]
-	(No symbol) [0x0x7ff654d5b17f]
-	(No symbol) [0x0x7ff654d833d0]
-	(No symbol) [0x0x7ff654d5af13]
-	(No symbol) [0x0x7ff654d24151]
-	(No symbol) [0x0x7ff654d24ee3]
-	GetHandleVerifier [0x0x7ff65520686d+2962461]
-	GetHandleVerifier [0x0x7ff655200b8d+2938685]
-	GetHandleVerifier [0x0x7ff65521f74d+3064573]
-	GetHandleVerifier [0x0x7ff654f60c9e+186446]
-	GetHandleVerifier [0x0x7ff654f68a6f+218655]
-	GetHandleVerifier [0x0x7ff654f4f944+115956]
-	GetHandleVerifier [0x0x7ff654f4faf9+116393]
-	GetHandleVerifier [0x0x7ff654f35f28+10968]
+	GetHandleVerifier [0x0x7ff76d756b55+79621]
+	GetHandleVerifier [0x0x7ff76d756bb0+79712]
+	(No symbol) [0x0x7ff76d4ec0ea]
+	(No symbol) [0x0x7ff76d542f56]
+	(No symbol) [0x0x7ff76d54320c]
+	(No symbol) [0x0x7ff76d5965b7]
+	(No symbol) [0x0x7ff76d56b17f]
+	(No symbol) [0x0x7ff76d5933d0]
+	(No symbol) [0x0x7ff76d56af13]
+	(No symbol) [0x0x7ff76d534151]
+	(No symbol) [0x0x7ff76d534ee3]
+	GetHandleVerifier [0x0x7ff76da1686d+2962461]
+	GetHandleVerifier [0x0x7ff76da10b8d+2938685]
+	GetHandleVerifier [0x0x7ff76da2f74d+3064573]
+	GetHandleVerifier [0x0x7ff76d770c9e+186446]
+	GetHandleVerifier [0x0x7ff76d778a6f+218655]
+	GetHandleVerifier [0x0x7ff76d75f944+115956]
+	GetHandleVerifier [0x0x7ff76d75faf9+116393]
+	GetHandleVerifier [0x0x7ff76d745f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff654f46b55+79621]
-	GetHandleVerifier [0x0x7ff654f46bb0+79712]
-	(No symbol) [0x0x7ff654cdc0ea]
-	(No symbol) [0x0x7ff654d32f56]
-	(No symbol) [0x0x7ff654d3320c]
-	(No symbol) [0x0x7ff654d865b7]
-	(No symbol) [0x0x7ff654d5b17f]
-	(No symbol) [0x0x7ff654d833d0]
-	(No symbol) [0x0x7ff654d5af13]
-	(No symbol) [0x0x7ff654d24151]
-	(No symbol) [0x0x7ff654d24ee3]
-	GetHandleVerifier [0x0x7ff65520686d+2962461]
-	GetHandleVerifier [0x0x7ff655200b8d+2938685]
-	GetHandleVerifier [0x0x7ff65521f74d+3064573]
-	GetHandleVerifier [0x0x7ff654f60c9e+186446]
-	GetHandleVerifier [0x0x7ff654f68a6f+218655]
-	GetHandleVerifier [0x0x7ff654f4f944+115956]
-	GetHandleVerifier [0x0x7ff654f4faf9+116393]
-	GetHandleVerifier [0x0x7ff654f35f28+10968]
+	GetHandleVerifier [0x0x7ff76d756b55+79621]
+	GetHandleVerifier [0x0x7ff76d756bb0+79712]
+	(No symbol) [0x0x7ff76d4ec0ea]
+	(No symbol) [0x0x7ff76d542f56]
+	(No symbol) [0x0x7ff76d54320c]
+	(No symbol) [0x0x7ff76d5965b7]
+	(No symbol) [0x0x7ff76d56b17f]
+	(No symbol) [0x0x7ff76d5933d0]
+	(No symbol) [0x0x7ff76d56af13]
+	(No symbol) [0x0x7ff76d534151]
+	(No symbol) [0x0x7ff76d534ee3]
+	GetHandleVerifier [0x0x7ff76da1686d+2962461]
+	GetHandleVerifier [0x0x7ff76da10b8d+2938685]
+	GetHandleVerifier [0x0x7ff76da2f74d+3064573]
+	GetHandleVerifier [0x0x7ff76d770c9e+186446]
+	GetHandleVerifier [0x0x7ff76d778a6f+218655]
+	GetHandleVerifier [0x0x7ff76d75f944+115956]
+	GetHandleVerifier [0x0x7ff76d75faf9+116393]
+	GetHandleVerifier [0x0x7ff76d745f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff654f46b55+79621]
-	GetHandleVerifier [0x0x7ff654f46bb0+79712]
-	(No symbol) [0x0x7ff654cdc0ea]
-	(No symbol) [0x0x7ff654d32f56]
-	(No symbol) [0x0x7ff654d3320c]
-	(No symbol) [0x0x7ff654d865b7]
-	(No symbol) [0x0x7ff654d5b17f]
-	(No symbol) [0x0x7ff654d833d0]
-	(No symbol) [0x0x7ff654d5af13]
-	(No symbol) [0x0x7ff654d24151]
-	(No symbol) [0x0x7ff654d24ee3]
-	GetHandleVerifier [0x0x7ff65520686d+2962461]
-	GetHandleVerifier [0x0x7ff655200b8d+2938685]
-	GetHandleVerifier [0x0x7ff65521f74d+3064573]
-	GetHandleVerifier [0x0x7ff654f60c9e+186446]
-	GetHandleVerifier [0x0x7ff654f68a6f+218655]
-	GetHandleVerifier [0x0x7ff654f4f944+115956]
-	GetHandleVerifier [0x0x7ff654f4faf9+116393]
-	GetHandleVerifier [0x0x7ff654f35f28+10968]
+	GetHandleVerifier [0x0x7ff76d756b55+79621]
+	GetHandleVerifier [0x0x7ff76d756bb0+79712]
+	(No symbol) [0x0x7ff76d4ec0ea]
+	(No symbol) [0x0x7ff76d542f56]
+	(No symbol) [0x0x7ff76d54320c]
+	(No symbol) [0x0x7ff76d5965b7]
+	(No symbol) [0x0x7ff76d56b17f]
+	(No symbol) [0x0x7ff76d5933d0]
+	(No symbol) [0x0x7ff76d56af13]
+	(No symbol) [0x0x7ff76d534151]
+	(No symbol) [0x0x7ff76d534ee3]
+	GetHandleVerifier [0x0x7ff76da1686d+2962461]
+	GetHandleVerifier [0x0x7ff76da10b8d+2938685]
+	GetHandleVerifier [0x0x7ff76da2f74d+3064573]
+	GetHandleVerifier [0x0x7ff76d770c9e+186446]
+	GetHandleVerifier [0x0x7ff76d778a6f+218655]
+	GetHandleVerifier [0x0x7ff76d75f944+115956]
+	GetHandleVerifier [0x0x7ff76d75faf9+116393]
+	GetHandleVerifier [0x0x7ff76d745f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff654f46b55+79621]
-	GetHandleVerifier [0x0x7ff654f46bb0+79712]
-	(No symbol) [0x0x7ff654cdc0ea]
-	(No symbol) [0x0x7ff654d32f56]
-	(No symbol) [0x0x7ff654d3320c]
-	(No symbol) [0x0x7ff654d865b7]
-	(No symbol) [0x0x7ff654d5b17f]
-	(No symbol) [0x0x7ff654d833d0]
-	(No symbol) [0x0x7ff654d5af13]
-	(No symbol) [0x0x7ff654d24151]
-	(No symbol) [0x0x7ff654d24ee3]
-	GetHandleVerifier [0x0x7ff65520686d+2962461]
-	GetHandleVerifier [0x0x7ff655200b8d+2938685]
-	GetHandleVerifier [0x0x7ff65521f74d+3064573]
-	GetHandleVerifier [0x0x7ff654f60c9e+186446]
-	GetHandleVerifier [0x0x7ff654f68a6f+218655]
-	GetHandleVerifier [0x0x7ff654f4f944+115956]
-	GetHandleVerifier [0x0x7ff654f4faf9+116393]
-	GetHandleVerifier [0x0x7ff654f35f28+10968]
+	GetHandleVerifier [0x0x7ff76d756b55+79621]
+	GetHandleVerifier [0x0x7ff76d756bb0+79712]
+	(No symbol) [0x0x7ff76d4ec0ea]
+	(No symbol) [0x0x7ff76d542f56]
+	(No symbol) [0x0x7ff76d54320c]
+	(No symbol) [0x0x7ff76d5965b7]
+	(No symbol) [0x0x7ff76d56b17f]
+	(No symbol) [0x0x7ff76d5933d0]
+	(No symbol) [0x0x7ff76d56af13]
+	(No symbol) [0x0x7ff76d534151]
+	(No symbol) [0x0x7ff76d534ee3]
+	GetHandleVerifier [0x0x7ff76da1686d+2962461]
+	GetHandleVerifier [0x0x7ff76da10b8d+2938685]
+	GetHandleVerifier [0x0x7ff76da2f74d+3064573]
+	GetHandleVerifier [0x0x7ff76d770c9e+186446]
+	GetHandleVerifier [0x0x7ff76d778a6f+218655]
+	GetHandleVerifier [0x0x7ff76d75f944+115956]
+	GetHandleVerifier [0x0x7ff76d75faf9+116393]
+	GetHandleVerifier [0x0x7ff76d745f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff654f46b55+79621]
-	GetHandleVerifier [0x0x7ff654f46bb0+79712]
-	(No symbol) [0x0x7ff654cdc0ea]
-	(No symbol) [0x0x7ff654d32f56]
-	(No symbol) [0x0x7ff654d3320c]
-	(No symbol) [0x0x7ff654d865b7]
-	(No symbol) [0x0x7ff654d5b17f]
-	(No symbol) [0x0x7ff654d833d0]
-	(No symbol) [0x0x7ff654d5af13]
-	(No symbol) [0x0x7ff654d24151]
-	(No symbol) [0x0x7ff654d24ee3]
-	GetHandleVerifier [0x0x7ff65520686d+2962461]
-	GetHandleVerifier [0x0x7ff655200b8d+2938685]
-	GetHandleVerifier [0x0x7ff65521f74d+3064573]
-	GetHandleVerifier [0x0x7ff654f60c9e+186446]
-	GetHandleVerifier [0x0x7ff654f68a6f+218655]
-	GetHandleVerifier [0x0x7ff654f4f944+115956]
-	GetHandleVerifier [0x0x7ff654f4faf9+116393]
-	GetHandleVerifier [0x0x7ff654f35f28+10968]
+	GetHandleVerifier [0x0x7ff76d756b55+79621]
+	GetHandleVerifier [0x0x7ff76d756bb0+79712]
+	(No symbol) [0x0x7ff76d4ec0ea]
+	(No symbol) [0x0x7ff76d542f56]
+	(No symbol) [0x0x7ff76d54320c]
+	(No symbol) [0x0x7ff76d5965b7]
+	(No symbol) [0x0x7ff76d56b17f]
+	(No symbol) [0x0x7ff76d5933d0]
+	(No symbol) [0x0x7ff76d56af13]
+	(No symbol) [0x0x7ff76d534151]
+	(No symbol) [0x0x7ff76d534ee3]
+	GetHandleVerifier [0x0x7ff76da1686d+2962461]
+	GetHandleVerifier [0x0x7ff76da10b8d+2938685]
+	GetHandleVerifier [0x0x7ff76da2f74d+3064573]
+	GetHandleVerifier [0x0x7ff76d770c9e+186446]
+	GetHandleVerifier [0x0x7ff76d778a6f+218655]
+	GetHandleVerifier [0x0x7ff76d75f944+115956]
+	GetHandleVerifier [0x0x7ff76d75faf9+116393]
+	GetHandleVerifier [0x0x7ff76d745f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff654f46b55+79621]
-	GetHandleVerifier [0x0x7ff654f46bb0+79712]
-	(No symbol) [0x0x7ff654cdc0ea]
-	(No symbol) [0x0x7ff654d32f56]
-	(No symbol) [0x0x7ff654d3320c]
-	(No symbol) [0x0x7ff654d865b7]
-	(No symbol) [0x0x7ff654d5b17f]
-	(No symbol) [0x0x7ff654d833d0]
-	(No symbol) [0x0x7ff654d5af13]
-	(No symbol) [0x0x7ff654d24151]
-	(No symbol) [0x0x7ff654d24ee3]
-	GetHandleVerifier [0x0x7ff65520686d+2962461]
-	GetHandleVerifier [0x0x7ff655200b8d+2938685]
-	GetHandleVerifier [0x0x7ff65521f74d+3064573]
-	GetHandleVerifier [0x0x7ff654f60c9e+186446]
-	GetHandleVerifier [0x0x7ff654f68a6f+218655]
-	GetHandleVerifier [0x0x7ff654f4f944+115956]
-	GetHandleVerifier [0x0x7ff654f4faf9+116393]
-	GetHandleVerifier [0x0x7ff654f35f28+10968]
+	GetHandleVerifier [0x0x7ff76d756b55+79621]
+	GetHandleVerifier [0x0x7ff76d756bb0+79712]
+	(No symbol) [0x0x7ff76d4ec0ea]
+	(No symbol) [0x0x7ff76d542f56]
+	(No symbol) [0x0x7ff76d54320c]
+	(No symbol) [0x0x7ff76d5965b7]
+	(No symbol) [0x0x7ff76d56b17f]
+	(No symbol) [0x0x7ff76d5933d0]
+	(No symbol) [0x0x7ff76d56af13]
+	(No symbol) [0x0x7ff76d534151]
+	(No symbol) [0x0x7ff76d534ee3]
+	GetHandleVerifier [0x0x7ff76da1686d+2962461]
+	GetHandleVerifier [0x0x7ff76da10b8d+2938685]
+	GetHandleVerifier [0x0x7ff76da2f74d+3064573]
+	GetHandleVerifier [0x0x7ff76d770c9e+186446]
+	GetHandleVerifier [0x0x7ff76d778a6f+218655]
+	GetHandleVerifier [0x0x7ff76d75f944+115956]
+	GetHandleVerifier [0x0x7ff76d75faf9+116393]
+	GetHandleVerifier [0x0x7ff76d745f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff654f46b55+79621]
-	GetHandleVerifier [0x0x7ff654f46bb0+79712]
-	(No symbol) [0x0x7ff654cdc0ea]
-	(No symbol) [0x0x7ff654d32f56]
-	(No symbol) [0x0x7ff654d3320c]
-	(No symbol) [0x0x7ff654d865b7]
-	(No symbol) [0x0x7ff654d5b17f]
-	(No symbol) [0x0x7ff654d833d0]
-	(No symbol) [0x0x7ff654d5af13]
-	(No symbol) [0x0x7ff654d24151]
-	(No symbol) [0x0x7ff654d24ee3]
-	GetHandleVerifier [0x0x7ff65520686d+2962461]
-	GetHandleVerifier [0x0x7ff655200b8d+2938685]
-	GetHandleVerifier [0x0x7ff65521f74d+3064573]
-	GetHandleVerifier [0x0x7ff654f60c9e+186446]
-	GetHandleVerifier [0x0x7ff654f68a6f+218655]
-	GetHandleVerifier [0x0x7ff654f4f944+115956]
-	GetHandleVerifier [0x0x7ff654f4faf9+116393]
-	GetHandleVerifier [0x0x7ff654f35f28+10968]
+	GetHandleVerifier [0x0x7ff76d756b55+79621]
+	GetHandleVerifier [0x0x7ff76d756bb0+79712]
+	(No symbol) [0x0x7ff76d4ec0ea]
+	(No symbol) [0x0x7ff76d542f56]
+	(No symbol) [0x0x7ff76d54320c]
+	(No symbol) [0x0x7ff76d5965b7]
+	(No symbol) [0x0x7ff76d56b17f]
+	(No symbol) [0x0x7ff76d5933d0]
+	(No symbol) [0x0x7ff76d56af13]
+	(No symbol) [0x0x7ff76d534151]
+	(No symbol) [0x0x7ff76d534ee3]
+	GetHandleVerifier [0x0x7ff76da1686d+2962461]
+	GetHandleVerifier [0x0x7ff76da10b8d+2938685]
+	GetHandleVerifier [0x0x7ff76da2f74d+3064573]
+	GetHandleVerifier [0x0x7ff76d770c9e+186446]
+	GetHandleVerifier [0x0x7ff76d778a6f+218655]
+	GetHandleVerifier [0x0x7ff76d75f944+115956]
+	GetHandleVerifier [0x0x7ff76d75faf9+116393]
+	GetHandleVerifier [0x0x7ff76d745f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff654f46b55+79621]
-	GetHandleVerifier [0x0x7ff654f46bb0+79712]
-	(No symbol) [0x0x7ff654cdc0ea]
-	(No symbol) [0x0x7ff654d32f56]
-	(No symbol) [0x0x7ff654d3320c]
-	(No symbol) [0x0x7ff654d865b7]
-	(No symbol) [0x0x7ff654d5b17f]
-	(No symbol) [0x0x7ff654d833d0]
-	(No symbol) [0x0x7ff654d5af13]
-	(No symbol) [0x0x7ff654d24151]
-	(No symbol) [0x0x7ff654d24ee3]
-	GetHandleVerifier [0x0x7ff65520686d+2962461]
-	GetHandleVerifier [0x0x7ff655200b8d+2938685]
-	GetHandleVerifier [0x0x7ff65521f74d+3064573]
-	GetHandleVerifier [0x0x7ff654f60c9e+186446]
-	GetHandleVerifier [0x0x7ff654f68a6f+218655]
-	GetHandleVerifier [0x0x7ff654f4f944+115956]
-	GetHandleVerifier [0x0x7ff654f4faf9+116393]
-	GetHandleVerifier [0x0x7ff654f35f28+10968]
+	GetHandleVerifier [0x0x7ff76d756b55+79621]
+	GetHandleVerifier [0x0x7ff76d756bb0+79712]
+	(No symbol) [0x0x7ff76d4ec0ea]
+	(No symbol) [0x0x7ff76d542f56]
+	(No symbol) [0x0x7ff76d54320c]
+	(No symbol) [0x0x7ff76d5965b7]
+	(No symbol) [0x0x7ff76d56b17f]
+	(No symbol) [0x0x7ff76d5933d0]
+	(No symbol) [0x0x7ff76d56af13]
+	(No symbol) [0x0x7ff76d534151]
+	(No symbol) [0x0x7ff76d534ee3]
+	GetHandleVerifier [0x0x7ff76da1686d+2962461]
+	GetHandleVerifier [0x0x7ff76da10b8d+2938685]
+	GetHandleVerifier [0x0x7ff76da2f74d+3064573]
+	GetHandleVerifier [0x0x7ff76d770c9e+186446]
+	GetHandleVerifier [0x0x7ff76d778a6f+218655]
+	GetHandleVerifier [0x0x7ff76d75f944+115956]
+	GetHandleVerifier [0x0x7ff76d75faf9+116393]
+	GetHandleVerifier [0x0x7ff76d745f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff654f46b55+79621]
-	GetHandleVerifier [0x0x7ff654f46bb0+79712]
-	(No symbol) [0x0x7ff654cdc0ea]
-	(No symbol) [0x0x7ff654d32f56]
-	(No symbol) [0x0x7ff654d3320c]
-	(No symbol) [0x0x7ff654d865b7]
-	(No symbol) [0x0x7ff654d5b17f]
-	(No symbol) [0x0x7ff654d833d0]
-	(No symbol) [0x0x7ff654d5af13]
-	(No symbol) [0x0x7ff654d24151]
-	(No symbol) [0x0x7ff654d24ee3]
-	GetHandleVerifier [0x0x7ff65520686d+2962461]
-	GetHandleVerifier [0x0x7ff655200b8d+2938685]
-	GetHandleVerifier [0x0x7ff65521f74d+3064573]
-	GetHandleVerifier [0x0x7ff654f60c9e+186446]
-	GetHandleVerifier [0x0x7ff654f68a6f+218655]
-	GetHandleVerifier [0x0x7ff654f4f944+115956]
-	GetHandleVerifier [0x0x7ff654f4faf9+116393]
-	GetHandleVerifier [0x0x7ff654f35f28+10968]
+	GetHandleVerifier [0x0x7ff76d756b55+79621]
+	GetHandleVerifier [0x0x7ff76d756bb0+79712]
+	(No symbol) [0x0x7ff76d4ec0ea]
+	(No symbol) [0x0x7ff76d542f56]
+	(No symbol) [0x0x7ff76d54320c]
+	(No symbol) [0x0x7ff76d5965b7]
+	(No symbol) [0x0x7ff76d56b17f]
+	(No symbol) [0x0x7ff76d5933d0]
+	(No symbol) [0x0x7ff76d56af13]
+	(No symbol) [0x0x7ff76d534151]
+	(No symbol) [0x0x7ff76d534ee3]
+	GetHandleVerifier [0x0x7ff76da1686d+2962461]
+	GetHandleVerifier [0x0x7ff76da10b8d+2938685]
+	GetHandleVerifier [0x0x7ff76da2f74d+3064573]
+	GetHandleVerifier [0x0x7ff76d770c9e+186446]
+	GetHandleVerifier [0x0x7ff76d778a6f+218655]
+	GetHandleVerifier [0x0x7ff76d75f944+115956]
+	GetHandleVerifier [0x0x7ff76d75faf9+116393]
+	GetHandleVerifier [0x0x7ff76d745f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff654f46b55+79621]
-	GetHandleVerifier [0x0x7ff654f46bb0+79712]
-	(No symbol) [0x0x7ff654cdc0ea]
-	(No symbol) [0x0x7ff654d32f56]
-	(No symbol) [0x0x7ff654d3320c]
-	(No symbol) [0x0x7ff654d865b7]
-	(No symbol) [0x0x7ff654d5b17f]
-	(No symbol) [0x0x7ff654d833d0]
-	(No symbol) [0x0x7ff654d5af13]
-	(No symbol) [0x0x7ff654d24151]
-	(No symbol) [0x0x7ff654d24ee3]
-	GetHandleVerifier [0x0x7ff65520686d+2962461]
-	GetHandleVerifier [0x0x7ff655200b8d+2938685]
-	GetHandleVerifier [0x0x7ff65521f74d+3064573]
-	GetHandleVerifier [0x0x7ff654f60c9e+186446]
-	GetHandleVerifier [0x0x7ff654f68a6f+218655]
-	GetHandleVerifier [0x0x7ff654f4f944+115956]
-	GetHandleVerifier [0x0x7ff654f4faf9+116393]
-	GetHandleVerifier [0x0x7ff654f35f28+10968]
+	GetHandleVerifier [0x0x7ff76d756b55+79621]
+	GetHandleVerifier [0x0x7ff76d756bb0+79712]
+	(No symbol) [0x0x7ff76d4ec0ea]
+	(No symbol) [0x0x7ff76d542f56]
+	(No symbol) [0x0x7ff76d54320c]
+	(No symbol) [0x0x7ff76d5965b7]
+	(No symbol) [0x0x7ff76d56b17f]
+	(No symbol) [0x0x7ff76d5933d0]
+	(No symbol) [0x0x7ff76d56af13]
+	(No symbol) [0x0x7ff76d534151]
+	(No symbol) [0x0x7ff76d534ee3]
+	GetHandleVerifier [0x0x7ff76da1686d+2962461]
+	GetHandleVerifier [0x0x7ff76da10b8d+2938685]
+	GetHandleVerifier [0x0x7ff76da2f74d+3064573]
+	GetHandleVerifier [0x0x7ff76d770c9e+186446]
+	GetHandleVerifier [0x0x7ff76d778a6f+218655]
+	GetHandleVerifier [0x0x7ff76d75f944+115956]
+	GetHandleVerifier [0x0x7ff76d75faf9+116393]
+	GetHandleVerifier [0x0x7ff76d745f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>£1160.0</t>
+          <t>£1152.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
